--- a/tabelas/tabelas_contingencia_mudanca_clusters.xlsx
+++ b/tabelas/tabelas_contingencia_mudanca_clusters.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_AD4D361C20488D9ACD6DCC2BF5D94BE65ADEDD9E" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{DBCFBD8B-54D9-45BF-8B44-7CB0316B2146}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_AD4D361C20488D9ACD6DCC2BF5D94BE65ADEDD9E" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{523B3442-6CC6-439C-BEB5-0FEA97E0530B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="45">
   <si>
     <t>Private healthcare and insurance</t>
   </si>
@@ -47,13 +47,121 @@
   </si>
   <si>
     <t>SUS</t>
+  </si>
+  <si>
+    <t>151 (2.7%)</t>
+  </si>
+  <si>
+    <t>177 (3.2%)</t>
+  </si>
+  <si>
+    <t>66 (1.2%)</t>
+  </si>
+  <si>
+    <t>140 (2.5%)</t>
+  </si>
+  <si>
+    <t>626 (11.2%)</t>
+  </si>
+  <si>
+    <t>528 (9.5%)</t>
+  </si>
+  <si>
+    <t>84 (1.5%)</t>
+  </si>
+  <si>
+    <t>509 (9.1%)</t>
+  </si>
+  <si>
+    <t>3288 (59%)</t>
+  </si>
+  <si>
+    <t>349 (6.3%)</t>
+  </si>
+  <si>
+    <t>418 (7.5%)</t>
+  </si>
+  <si>
+    <t>129 (2.3%)</t>
+  </si>
+  <si>
+    <t>242 (4.3%)</t>
+  </si>
+  <si>
+    <t>1240 (22.3%)</t>
+  </si>
+  <si>
+    <t>728 (13.1%)</t>
+  </si>
+  <si>
+    <t>77 (1.4%)</t>
+  </si>
+  <si>
+    <t>649 (11.7%)</t>
+  </si>
+  <si>
+    <t>1738 (31.2%)</t>
+  </si>
+  <si>
+    <t>42 (0.8%)</t>
+  </si>
+  <si>
+    <t>156 (2.8%)</t>
+  </si>
+  <si>
+    <t>697 (12.5%)</t>
+  </si>
+  <si>
+    <t>163 (2.9%)</t>
+  </si>
+  <si>
+    <t>519 (9.3%)</t>
+  </si>
+  <si>
+    <t>1528 (27.4%)</t>
+  </si>
+  <si>
+    <t>189 (3.4%)</t>
+  </si>
+  <si>
+    <t>619 (11.1%)</t>
+  </si>
+  <si>
+    <t>1656 (29.7%)</t>
+  </si>
+  <si>
+    <t>22 (0.4%)</t>
+  </si>
+  <si>
+    <t>85 (1.5%)</t>
+  </si>
+  <si>
+    <t>561 (10.1%)</t>
+  </si>
+  <si>
+    <t>146 (2.6%)</t>
+  </si>
+  <si>
+    <t>545 (9.8%)</t>
+  </si>
+  <si>
+    <t>1616 (29%)</t>
+  </si>
+  <si>
+    <t>207 (3.7%)</t>
+  </si>
+  <si>
+    <t>682 (12.2%)</t>
+  </si>
+  <si>
+    <t>1705 (30.6%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +171,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -198,18 +314,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -223,6 +330,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -513,291 +630,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <v>554</v>
-      </c>
-      <c r="C4" s="7">
-        <v>124</v>
-      </c>
-      <c r="D4" s="8">
-        <v>616</v>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
-        <v>3332</v>
-      </c>
-      <c r="C5" s="10">
-        <v>73</v>
-      </c>
-      <c r="D5" s="11">
-        <v>476</v>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
-        <v>69</v>
-      </c>
-      <c r="C6" s="13">
-        <v>132</v>
-      </c>
-      <c r="D6" s="14">
-        <v>193</v>
+      <c r="B6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="6">
-        <v>71</v>
-      </c>
-      <c r="C10" s="7">
-        <v>552</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1841</v>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="9">
-        <v>212</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1145</v>
-      </c>
-      <c r="D11" s="11">
-        <v>853</v>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="12">
-        <v>325</v>
-      </c>
-      <c r="C12" s="13">
-        <v>423</v>
-      </c>
-      <c r="D12" s="14">
-        <v>148</v>
+      <c r="B12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="6">
-        <v>619</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1656</v>
-      </c>
-      <c r="D16" s="8">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="9">
-        <v>519</v>
-      </c>
-      <c r="C17" s="10">
-        <v>1528</v>
-      </c>
-      <c r="D17" s="11">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="B17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="12">
-        <v>156</v>
-      </c>
-      <c r="C18" s="13">
-        <v>697</v>
-      </c>
-      <c r="D18" s="14">
+      <c r="B18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="6">
-        <v>522</v>
-      </c>
-      <c r="C22" s="7">
-        <v>19</v>
-      </c>
-      <c r="D22" s="8">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="9">
-        <v>1524</v>
-      </c>
-      <c r="C23" s="10">
-        <v>115</v>
-      </c>
-      <c r="D23" s="11">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="12">
-        <v>1909</v>
-      </c>
-      <c r="C24" s="13">
-        <v>195</v>
-      </c>
-      <c r="D24" s="14">
-        <v>737</v>
+      <c r="C24" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
